--- a/erp_sales.xlsx
+++ b/erp_sales.xlsx
@@ -637,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I513"/>
+  <dimension ref="A1:I519"/>
   <cols>
     <col min="1" max="1" width="16.6640625" customWidth="1" style="0"/>
     <col min="2" max="2" width="16.6640625" customWidth="1" style="0"/>
@@ -19509,74 +19509,296 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="10" t="inlineStr">
+      <c r="A511" s="6" t="inlineStr">
+        <is>
+          <t>2026/05/28 -1</t>
+        </is>
+      </c>
+      <c r="B511" s="7" t="inlineStr">
+        <is>
+          <t>A0001</t>
+        </is>
+      </c>
+      <c r="C511" s="8" t="inlineStr">
+        <is>
+          <t>유월의보리 볶음소스 [5KG]</t>
+        </is>
+      </c>
+      <c r="D511" s="9">
+        <v>2</v>
+      </c>
+      <c r="E511" s="9">
+        <v>41700</v>
+      </c>
+      <c r="F511" s="9">
+        <v>83400</v>
+      </c>
+      <c r="G511" s="9">
+        <v>8340</v>
+      </c>
+      <c r="H511" s="9">
+        <v>91740</v>
+      </c>
+      <c r="I511" s="8" t="inlineStr">
+        <is>
+          <t>유월의보리 양재점</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="6" t="inlineStr">
+        <is>
+          <t>2026/05/28 -1</t>
+        </is>
+      </c>
+      <c r="B512" s="7" t="inlineStr">
+        <is>
+          <t>A0003</t>
+        </is>
+      </c>
+      <c r="C512" s="8" t="inlineStr">
+        <is>
+          <t>유월의보리 청국장 소스 [5KG]</t>
+        </is>
+      </c>
+      <c r="D512" s="9">
+        <v>6</v>
+      </c>
+      <c r="E512" s="9">
+        <v>26800</v>
+      </c>
+      <c r="F512" s="9">
+        <v>160800</v>
+      </c>
+      <c r="G512" s="9">
+        <v>16080</v>
+      </c>
+      <c r="H512" s="9">
+        <v>176880</v>
+      </c>
+      <c r="I512" s="8" t="inlineStr">
+        <is>
+          <t>유월의보리 양재점</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="6" t="inlineStr">
+        <is>
+          <t>2026/05/28 -1</t>
+        </is>
+      </c>
+      <c r="B513" s="7" t="inlineStr">
+        <is>
+          <t>A0008</t>
+        </is>
+      </c>
+      <c r="C513" s="8" t="inlineStr">
+        <is>
+          <t>유월의보리 바지락칼국수 소스 [5KG]</t>
+        </is>
+      </c>
+      <c r="D513" s="9">
+        <v>2</v>
+      </c>
+      <c r="E513" s="9">
+        <v>20835</v>
+      </c>
+      <c r="F513" s="9">
+        <v>41670</v>
+      </c>
+      <c r="G513" s="9">
+        <v>4167</v>
+      </c>
+      <c r="H513" s="9">
+        <v>45837</v>
+      </c>
+      <c r="I513" s="8" t="inlineStr">
+        <is>
+          <t>유월의보리 양재점</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="6" t="inlineStr">
+        <is>
+          <t>2026/05/28 -1</t>
+        </is>
+      </c>
+      <c r="B514" s="7" t="inlineStr">
+        <is>
+          <t>A0012</t>
+        </is>
+      </c>
+      <c r="C514" s="8" t="inlineStr">
+        <is>
+          <t>유월의보리 유자연근장아찌 [5KG]</t>
+        </is>
+      </c>
+      <c r="D514" s="9">
+        <v>4</v>
+      </c>
+      <c r="E514" s="9">
+        <v>43200</v>
+      </c>
+      <c r="F514" s="9">
+        <v>172800</v>
+      </c>
+      <c r="G514" s="9">
+        <v>17280</v>
+      </c>
+      <c r="H514" s="9">
+        <v>190080</v>
+      </c>
+      <c r="I514" s="8" t="inlineStr">
+        <is>
+          <t>유월의보리 양재점</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="6" t="inlineStr">
+        <is>
+          <t>2026/05/28 -1</t>
+        </is>
+      </c>
+      <c r="B515" s="7" t="inlineStr">
+        <is>
+          <t>A0018</t>
+        </is>
+      </c>
+      <c r="C515" s="8" t="inlineStr">
+        <is>
+          <t>유월의보리 조미보리 [3KG]</t>
+        </is>
+      </c>
+      <c r="D515" s="9">
+        <v>12</v>
+      </c>
+      <c r="E515" s="9">
+        <v>13500</v>
+      </c>
+      <c r="F515" s="9">
+        <v>162000</v>
+      </c>
+      <c r="G515" s="9">
+        <v>16200</v>
+      </c>
+      <c r="H515" s="9">
+        <v>178200</v>
+      </c>
+      <c r="I515" s="8" t="inlineStr">
+        <is>
+          <t>유월의보리 양재점</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="6" t="inlineStr">
+        <is>
+          <t>2026/05/28 -1</t>
+        </is>
+      </c>
+      <c r="B516" s="7" t="inlineStr">
+        <is>
+          <t>A0034</t>
+        </is>
+      </c>
+      <c r="C516" s="8" t="inlineStr">
+        <is>
+          <t>경기미 [20KG]</t>
+        </is>
+      </c>
+      <c r="D516" s="9">
+        <v>2</v>
+      </c>
+      <c r="E516" s="9">
+        <v>65000</v>
+      </c>
+      <c r="F516" s="9">
+        <v>130000</v>
+      </c>
+      <c r="G516" s="9">
+        <v>13000</v>
+      </c>
+      <c r="H516" s="9">
+        <v>143000</v>
+      </c>
+      <c r="I516" s="8" t="inlineStr">
+        <is>
+          <t>유월의보리 양재점</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="10" t="inlineStr">
         <is>
           <t>2026/05  계</t>
         </is>
       </c>
-      <c r="B511" s="5"/>
-      <c r="C511" s="5"/>
-      <c r="D511" s="11">
-        <v>2001</v>
-      </c>
-      <c r="E511" s="11">
-        <v>18213520</v>
-      </c>
-      <c r="F511" s="11">
-        <v>60374726</v>
-      </c>
-      <c r="G511" s="11">
-        <v>6032882</v>
-      </c>
-      <c r="H511" s="11">
-        <v>66407608</v>
-      </c>
-      <c r="I511" s="5"/>
-    </row>
-    <row r="512">
-      <c r="A512" s="10" t="inlineStr">
+      <c r="B517" s="5"/>
+      <c r="C517" s="5"/>
+      <c r="D517" s="11">
+        <v>2029</v>
+      </c>
+      <c r="E517" s="11">
+        <v>18424555</v>
+      </c>
+      <c r="F517" s="11">
+        <v>61125396</v>
+      </c>
+      <c r="G517" s="11">
+        <v>6107949</v>
+      </c>
+      <c r="H517" s="11">
+        <v>67233345</v>
+      </c>
+      <c r="I517" s="5"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="10" t="inlineStr">
         <is>
           <t>총합계</t>
         </is>
       </c>
-      <c r="B512" s="5"/>
-      <c r="C512" s="5"/>
-      <c r="D512" s="11">
-        <v>2001</v>
-      </c>
-      <c r="E512" s="11">
-        <v>18213520</v>
-      </c>
-      <c r="F512" s="11">
-        <v>60374726</v>
-      </c>
-      <c r="G512" s="11">
-        <v>6032882</v>
-      </c>
-      <c r="H512" s="11">
-        <v>66407608</v>
-      </c>
-      <c r="I512" s="5"/>
-    </row>
-    <row r="513">
-      <c r="A513" s="12" t="inlineStr">
-        <is>
-          <t>2026/05/28 (목) 오전 9:37:28</t>
-        </is>
-      </c>
-      <c r="B513" s="2"/>
-      <c r="C513" s="2"/>
-      <c r="D513" s="2"/>
-      <c r="E513" s="2"/>
-      <c r="F513" s="2"/>
-      <c r="G513" s="2"/>
-      <c r="H513" s="2"/>
-      <c r="I513" s="2"/>
+      <c r="B518" s="5"/>
+      <c r="C518" s="5"/>
+      <c r="D518" s="11">
+        <v>2029</v>
+      </c>
+      <c r="E518" s="11">
+        <v>18424555</v>
+      </c>
+      <c r="F518" s="11">
+        <v>61125396</v>
+      </c>
+      <c r="G518" s="11">
+        <v>6107949</v>
+      </c>
+      <c r="H518" s="11">
+        <v>67233345</v>
+      </c>
+      <c r="I518" s="5"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="12" t="inlineStr">
+        <is>
+          <t>2026/05/28 (목) 오후 12:36:19</t>
+        </is>
+      </c>
+      <c r="B519" s="2"/>
+      <c r="C519" s="2"/>
+      <c r="D519" s="2"/>
+      <c r="E519" s="2"/>
+      <c r="F519" s="2"/>
+      <c r="G519" s="2"/>
+      <c r="H519" s="2"/>
+      <c r="I519" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A511:C511"/>
-    <mergeCell ref="A512:C512"/>
+    <mergeCell ref="A517:C517"/>
+    <mergeCell ref="A518:C518"/>
   </mergeCells>
 </worksheet>
 </file>